--- a/Missing_Months_FY11-FY26.xlsx
+++ b/Missing_Months_FY11-FY26.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2164,16 +2164,16 @@
         <v>2026</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -2188,51 +2188,11 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Future board meeting (~2026-05-19); will appear in the meeting that approves the Mar 2026 register</t>
+          <t>Future board meeting</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Not yet held</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>Future board meeting</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2604,17 +2564,17 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>In progress — complete through May 2026; Jun 2026 register not yet approved</t>
         </is>
       </c>
     </row>
@@ -2632,13 +2592,13 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
     </row>
@@ -2732,17 +2692,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>RECOVERED — downloaded to BoardDocs_PDFs/</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2780,17 +2736,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>LISTED BUT FILE INACCESSIBLE (HTTP 404)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2804,17 +2756,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>NOT IN BOARDDOCS PUBLIC FEED</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2852,10 +2800,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -2868,10 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -2895,7 +2837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3034,6 +2976,66 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This audit counts months whose CHECK REGISTER is unavailable on BoardDocs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>It is NOT the same as fiscal-year transaction coverage: a register covers 1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>months of prior activity, so a missing register often leaves no gap in the data</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>(adjacent registers carry those dates). FY24 is the clearest case — the Nov 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>register was never posted, yet FY24 has full transaction coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>For fiscal-year coverage see project_docs/INDEX.md 'Coverage by fiscal year'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fiscal year = Michigan Jul 1 - Jun 30, attributed by issue date. Updated 2026-07-27.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
